--- a/master/result/09_深海传说：银色海豚/09_银色海豚.xlsx
+++ b/master/result/09_深海传说：银色海豚/09_银色海豚.xlsx
@@ -397,511 +397,647 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:D45"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>airport</v>
       </c>
       <c r="B2" t="str">
-        <v>airport</v>
+        <v>/ˈeəpɔːt/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>机场</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>ticket</v>
       </c>
       <c r="B3" t="str">
-        <v>ticket</v>
+        <v>/ticket/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>票</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>silver</v>
       </c>
       <c r="B4" t="str">
-        <v>silver</v>
+        <v>/silver/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>银</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>ocean</v>
       </c>
       <c r="B5" t="str">
-        <v>ocean</v>
+        <v>/ocean/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>海洋</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>critic</v>
       </c>
       <c r="B6" t="str">
-        <v>critic</v>
+        <v>/ˈkrɪtɪk/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>评论家</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>misery</v>
       </c>
       <c r="B7" t="str">
-        <v>misery</v>
+        <v>/misery/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>痛苦</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>driver</v>
       </c>
       <c r="B8" t="str">
-        <v>driver</v>
+        <v>/driver/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>驾驶员</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>table</v>
       </c>
       <c r="B9" t="str">
-        <v>table</v>
+        <v>/table/</v>
       </c>
       <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>桌子</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>symbol</v>
       </c>
       <c r="B10" t="str">
-        <v>symbol</v>
+        <v>/symbol/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>象征</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>historian</v>
       </c>
       <c r="B11" t="str">
-        <v>historian</v>
+        <v>/historian/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>历史学家</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>transition</v>
       </c>
       <c r="B12" t="str">
-        <v>transition</v>
+        <v>/transition/</v>
       </c>
       <c r="C12" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>转变</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>deceive</v>
       </c>
       <c r="B13" t="str">
-        <v>deceive</v>
+        <v>/deceive/</v>
       </c>
       <c r="C13" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D13" t="str">
         <v>欺骗</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>essential</v>
       </c>
       <c r="B14" t="str">
-        <v>essential</v>
+        <v>/essential/</v>
       </c>
       <c r="C14" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>本质</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>sponge</v>
       </c>
       <c r="B15" t="str">
-        <v>sponge</v>
+        <v>/sponge/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>海绵</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>mere</v>
       </c>
       <c r="B16" t="str">
-        <v>mere</v>
+        <v>/mere/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>仅仅</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>pie</v>
       </c>
       <c r="B17" t="str">
-        <v>pie</v>
+        <v>/pie/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>馅饼</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>clue</v>
       </c>
       <c r="B18" t="str">
-        <v>clue</v>
+        <v>/kluː/</v>
       </c>
       <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>线索</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>direction</v>
       </c>
       <c r="B19" t="str">
-        <v>direction</v>
+        <v>/direction/</v>
       </c>
       <c r="C19" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>方向</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>circuit</v>
       </c>
       <c r="B20" t="str">
-        <v>circuit</v>
+        <v>/circuit/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>回路</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>contemporary</v>
       </c>
       <c r="B21" t="str">
-        <v>contemporary</v>
+        <v>/kənˈtempərəri/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>现代</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>upright</v>
       </c>
       <c r="B22" t="str">
-        <v>upright</v>
+        <v>/upright/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>正直</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>conversion</v>
       </c>
       <c r="B23" t="str">
-        <v>conversion</v>
+        <v>/kənˈvɜːʃn/</v>
       </c>
       <c r="C23" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>转变</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>banquet</v>
       </c>
       <c r="B24" t="str">
-        <v>banquet</v>
+        <v>/banquet/</v>
       </c>
       <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>宴会</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>friendship</v>
       </c>
       <c r="B25" t="str">
-        <v>friendship</v>
+        <v>/friendship/</v>
       </c>
       <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>友谊</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>enrich</v>
       </c>
       <c r="B26" t="str">
-        <v>enrich</v>
+        <v>/enrich/</v>
       </c>
       <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>丰富</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>fascinate</v>
       </c>
       <c r="B27" t="str">
-        <v>fascinate</v>
+        <v>/fascinate/</v>
       </c>
       <c r="C27" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D27" t="str">
         <v>迷人</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>delight</v>
       </c>
       <c r="B28" t="str">
-        <v>delight</v>
+        <v>/delight/</v>
       </c>
       <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>快乐</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>total</v>
       </c>
       <c r="B29" t="str">
-        <v>total</v>
+        <v>/total/</v>
       </c>
       <c r="C29" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D29" t="str">
         <v>总共</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>rough</v>
       </c>
       <c r="B30" t="str">
-        <v>rough</v>
+        <v>/rough/</v>
       </c>
       <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>艰难</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>opinion</v>
       </c>
       <c r="B31" t="str">
-        <v>opinion</v>
+        <v>/opinion/</v>
       </c>
       <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>看法</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>liner</v>
       </c>
       <c r="B32" t="str">
-        <v>liner</v>
+        <v>/liner/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>班机</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>incur</v>
       </c>
       <c r="B33" t="str">
-        <v>incur</v>
+        <v>/incur/</v>
       </c>
       <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>招致</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>fabricate</v>
       </c>
       <c r="B34" t="str">
-        <v>fabricate</v>
+        <v>/fabricate/</v>
       </c>
       <c r="C34" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D34" t="str">
         <v>编造</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>guilt</v>
       </c>
       <c r="B35" t="str">
-        <v>guilt</v>
+        <v>/guilt/</v>
       </c>
       <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>内疚</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>imagination</v>
       </c>
       <c r="B36" t="str">
-        <v>imagination</v>
+        <v>/imagination/</v>
       </c>
       <c r="C36" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>想象力</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>offensive</v>
       </c>
       <c r="B37" t="str">
-        <v>offensive</v>
+        <v>/offensive/</v>
       </c>
       <c r="C37" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D37" t="str">
         <v>冒犯</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>settlement</v>
       </c>
       <c r="B38" t="str">
-        <v>settlement</v>
+        <v>/settlement/</v>
       </c>
       <c r="C38" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D38" t="str">
         <v>定居</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>locate</v>
       </c>
       <c r="B39" t="str">
-        <v>locate</v>
+        <v>/ləʊˈkeɪt/</v>
       </c>
       <c r="C39" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D39" t="str">
         <v>位于</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>labor</v>
       </c>
       <c r="B40" t="str">
-        <v>labor</v>
+        <v>/labor/</v>
       </c>
       <c r="C40" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D40" t="str">
         <v>劳动</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>stumble</v>
       </c>
       <c r="B41" t="str">
-        <v>stumble</v>
+        <v>/stumble/</v>
       </c>
       <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
         <v>绊倒</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>triangle</v>
       </c>
       <c r="B42" t="str">
-        <v>triangle</v>
+        <v>/triangle/</v>
       </c>
       <c r="C42" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D42" t="str">
         <v>三角形</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>party</v>
       </c>
       <c r="B43" t="str">
-        <v>party</v>
+        <v>/party/</v>
       </c>
       <c r="C43" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D43" t="str">
         <v>聚会</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>meaning</v>
       </c>
       <c r="B44" t="str">
-        <v>meaning</v>
+        <v>/meaning/</v>
       </c>
       <c r="C44" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D44" t="str">
         <v>意义</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>sister</v>
       </c>
       <c r="B45" t="str">
-        <v>sister</v>
+        <v>/sister/</v>
       </c>
       <c r="C45" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D45" t="str">
         <v>姐妹</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D45"/>
   </ignoredErrors>
 </worksheet>
 </file>